--- a/SHET/ZP001/zpoo1.xlsx
+++ b/SHET/ZP001/zpoo1.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08FC0DB-3CA1-4F24-BFAC-F4F5CF17017F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Лист1" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Info" state="visible" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Info" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>Ток</t>
-  </si>
-  <si>
-    <t>Воздействие</t>
-  </si>
-  <si>
-    <t>Контр. сигнал</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>Уставка I&gt;, А</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Iмакс, А</t>
   </si>
   <si>
-    <t>ОО</t>
-  </si>
-  <si>
     <t>X:41, X:42</t>
   </si>
   <si>
@@ -66,19 +63,37 @@
   </si>
   <si>
     <t>zpoo1</t>
+  </si>
+  <si>
+    <t>Вход для проверки</t>
+  </si>
+  <si>
+    <t>Сигнал</t>
+  </si>
+  <si>
+    <t>Выход для контроля</t>
+  </si>
+  <si>
+    <t>Iоо</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>ТС</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -105,18 +120,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -452,125 +470,157 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.714285714285714" customWidth="1"/>
-    <col min="2" max="2" width="23.571428571428573" customWidth="1"/>
-    <col min="3" max="3" width="18.285714285714285" customWidth="1"/>
-    <col min="4" max="4" width="26.142857142857142" customWidth="1"/>
-    <col min="5" max="5" width="21.428571428571427" customWidth="1"/>
-    <col min="6" max="6" width="22.285714285714285" customWidth="1"/>
-    <col min="7" max="7" width="16.428571428571427" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="13.714285714285714" customWidth="1"/>
-    <col min="10" max="10" width="11.714285714285714" customWidth="1"/>
-    <col min="11" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" customWidth="1"/>
+    <col min="11" max="24" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3"/>
       <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.571428571428573" customWidth="1"/>
-    <col min="2" max="2" width="42.142857142857146" customWidth="1"/>
-    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="2" max="2" width="42.140625" customWidth="1"/>
+    <col min="3" max="24" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>